--- a/input data/economics_in.xlsx
+++ b/input data/economics_in.xlsx
@@ -8,25 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris.seaman\Desktop\GitRepos\burnet-hbv\input data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFCC42C8-C94D-4556-B61D-CFA864D724E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC47E65-86DC-4CC8-8174-359FF69EAD67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-7720" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="costs" sheetId="1" r:id="rId1"/>
     <sheet name="qalys" sheetId="2" r:id="rId2"/>
+    <sheet name="productivity" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="65">
   <si>
     <t>par</t>
   </si>
@@ -85,14 +97,160 @@
     <t>treat_price</t>
   </si>
   <si>
-    <t>stat_year_life</t>
+    <t>annual_salary</t>
+  </si>
+  <si>
+    <t>etp_ratio</t>
+  </si>
+  <si>
+    <t>atsi_0-14_M</t>
+  </si>
+  <si>
+    <t>atsi_15-64_M</t>
+  </si>
+  <si>
+    <t>atsi_65+_M</t>
+  </si>
+  <si>
+    <t>atsi_0-14_F</t>
+  </si>
+  <si>
+    <t>atsi_15-64_F</t>
+  </si>
+  <si>
+    <t>atsi_65+_F</t>
+  </si>
+  <si>
+    <t>ausb_0-14_M</t>
+  </si>
+  <si>
+    <t>ausb_15-64_M</t>
+  </si>
+  <si>
+    <t>ausb_65+_M</t>
+  </si>
+  <si>
+    <t>ausb_0-14_F</t>
+  </si>
+  <si>
+    <t>ausb_15-64_F</t>
+  </si>
+  <si>
+    <t>ausb_65+_F</t>
+  </si>
+  <si>
+    <t>lros_0-14_M</t>
+  </si>
+  <si>
+    <t>lros_15-64_M</t>
+  </si>
+  <si>
+    <t>lros_65+_M</t>
+  </si>
+  <si>
+    <t>lros_0-14_F</t>
+  </si>
+  <si>
+    <t>lros_15-64_F</t>
+  </si>
+  <si>
+    <t>lros_65+_F</t>
+  </si>
+  <si>
+    <t>hros_0-14_M</t>
+  </si>
+  <si>
+    <t>hros_15-64_M</t>
+  </si>
+  <si>
+    <t>hros_65+_M</t>
+  </si>
+  <si>
+    <t>hros_0-14_F</t>
+  </si>
+  <si>
+    <t>hros_15-64_F</t>
+  </si>
+  <si>
+    <t>hros_65+_F</t>
+  </si>
+  <si>
+    <t>ypll_1519</t>
+  </si>
+  <si>
+    <t>dp_1519</t>
+  </si>
+  <si>
+    <t>ypll_2024</t>
+  </si>
+  <si>
+    <t>dp_2024</t>
+  </si>
+  <si>
+    <t>ypll_2529</t>
+  </si>
+  <si>
+    <t>dp_2529</t>
+  </si>
+  <si>
+    <t>ypll_3034</t>
+  </si>
+  <si>
+    <t>dp_3034</t>
+  </si>
+  <si>
+    <t>ypll_3539</t>
+  </si>
+  <si>
+    <t>dp_3539</t>
+  </si>
+  <si>
+    <t>ypll_4044</t>
+  </si>
+  <si>
+    <t>dp_4044</t>
+  </si>
+  <si>
+    <t>ypll_4549</t>
+  </si>
+  <si>
+    <t>dp_4549</t>
+  </si>
+  <si>
+    <t>ypll_5054</t>
+  </si>
+  <si>
+    <t>dp_5054</t>
+  </si>
+  <si>
+    <t>ypll_5559</t>
+  </si>
+  <si>
+    <t>dp_5559</t>
+  </si>
+  <si>
+    <t>ypll_6064</t>
+  </si>
+  <si>
+    <t>dp_6064</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,16 +276,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -406,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.36328125" bestFit="1" customWidth="1"/>
@@ -643,20 +805,9 @@
         <v>539.35583333333329</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22">
-        <v>253000</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Code names must be unique" error="Parameter code names must be unique" sqref="A9:A20 A22" xr:uid="{5FDA93C6-3E98-425E-94BE-B43F987A104A}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Code names must be unique" error="Parameter code names must be unique" sqref="A9:A20" xr:uid="{5FDA93C6-3E98-425E-94BE-B43F987A104A}">
       <formula1>COUNTIF(A:A,A9)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -848,4 +999,1809 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E20607A-F9A3-45A4-A461-06AE926A2BFB}">
+  <dimension ref="A1:Y23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S1" t="s">
+        <v>38</v>
+      </c>
+      <c r="T1" t="s">
+        <v>39</v>
+      </c>
+      <c r="U1" t="s">
+        <v>40</v>
+      </c>
+      <c r="V1" t="s">
+        <v>41</v>
+      </c>
+      <c r="W1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <f>2083.7*52</f>
+        <v>108352.4</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <f>2083.7*52</f>
+        <v>108352.4</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <f>2083.7*52</f>
+        <v>108352.4</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2">
+        <f>2083.7*52</f>
+        <v>108352.4</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2">
+        <f>2083.7*52</f>
+        <v>108352.4</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2">
+        <f>2083.7*52</f>
+        <v>108352.4</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2">
+        <f>2083.7*52</f>
+        <v>108352.4</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2" s="2">
+        <f>2083.7*52</f>
+        <v>108352.4</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3" s="3">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3" s="3">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3" s="3">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>46.8</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>46.8</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>46.8</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>46.8</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>46.8</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>46.8</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>46.8</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>46.8</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>1.2463777147664601E-3</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>8.4595862493270786E-4</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1.2463777147664601E-3</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>8.4595862493270786E-4</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>1.2463777147664601E-3</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>8.4595862493270786E-4</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1.2463777147664601E-3</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>8.4595862493270786E-4</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>41.8</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>41.8</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>41.8</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>41.8</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>41.8</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>41.8</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>41.8</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>41.8</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>2.3992771009254356E-3</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>3.5376451588095058E-3</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>2.3992771009254356E-3</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>3.5376451588095058E-3</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>2.3992771009254356E-3</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>3.5376451588095058E-3</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>2.3992771009254356E-3</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>3.5376451588095058E-3</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>6.4500046739164301E-3</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>7.9212489425517195E-3</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>6.4500046739164301E-3</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>7.9212489425517195E-3</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>6.4500046739164301E-3</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>7.9212489425517195E-3</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>6.4500046739164301E-3</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>7.9212489425517195E-3</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>31.8</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>31.8</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>31.8</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>31.8</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>31.8</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>31.8</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>31.8</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>31.8</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>2.1749291122674728E-2</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>2.2148734907329076E-2</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>2.1749291122674728E-2</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>2.2148734907329076E-2</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>2.1749291122674728E-2</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>2.2148734907329076E-2</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>2.1749291122674728E-2</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>2.2148734907329076E-2</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>26.8</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>26.8</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>26.8</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>26.8</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>26.8</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>26.8</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>26.8</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>26.8</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>4.2968871716573702E-2</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>5.1218949473198494E-2</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>4.2968871716573702E-2</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>5.1218949473198494E-2</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>4.2968871716573702E-2</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>5.1218949473198494E-2</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>4.2968871716573702E-2</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>5.1218949473198494E-2</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>21.8</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>21.8</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>21.8</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>21.8</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>21.8</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>21.8</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>21.8</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>21.8</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>7.9487738759230986E-2</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>9.8361916480812106E-2</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>7.9487738759230986E-2</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>9.8361916480812106E-2</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>7.9487738759230986E-2</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>9.8361916480812106E-2</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>7.9487738759230986E-2</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>9.8361916480812106E-2</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>16.8</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>16.8</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>16.8</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>16.8</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>16.8</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>16.8</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>16.8</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>16.8</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0.13351821269435701</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0.14711989540875181</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0.13351821269435701</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0.14711989540875181</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0.13351821269435701</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0.14711989540875181</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0.13351821269435701</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0.14711989540875181</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>11.8</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>11.8</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>11.8</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>11.8</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>11.8</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>11.8</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>11.8</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>11.8</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0.19751970834761473</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0.19803122356379296</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0.19751970834761473</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0.19803122356379296</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0.19751970834761473</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0.19803122356379296</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0.19751970834761473</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0.19803122356379296</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>6.8</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>6.8</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>6.8</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>6.8</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>6.8</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>6.8</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>6.8</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>6.8</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0.24104945003583336</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0.22494808890256093</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0.24104945003583336</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0.22494808890256093</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0.24104945003583336</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0.22494808890256093</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0.24104945003583336</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0.22494808890256093</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>1.8</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>1.8</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>1.8</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>1.8</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>1.8</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>1.8</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>1.8</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>1.8</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0.2736110678341071</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0.24586633853726061</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0.2736110678341071</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0.24586633853726061</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0.2736110678341071</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0.24586633853726061</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0.2736110678341071</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0.24586633853726061</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Code names must be unique" error="Parameter code names must be unique" sqref="A2:A23" xr:uid="{FAED26BF-DA04-45A2-847E-A6D53C9DB1EB}">
+      <formula1>COUNTIF(A:A,A2)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>